--- a/data_src/feed_posts.xlsx
+++ b/data_src/feed_posts.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20120" windowHeight="11030"/>
+    <workbookView windowWidth="16550" windowHeight="10370"/>
   </bookViews>
   <sheets>
-    <sheet name="feed_posts" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,24 +27,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="51">
   <si>
     <t>post_id</t>
   </si>
   <si>
-    <t>chapter_id</t>
+    <t>type</t>
+  </si>
+  <si>
+    <t>condition_id</t>
   </si>
   <si>
     <t>level_id</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
     <t>text</t>
   </si>
   <si>
+    <t>avatar_path</t>
+  </si>
+  <si>
     <t>image_path</t>
   </si>
   <si>
-    <t>avatar_path</t>
+    <t>image_path2</t>
   </si>
   <si>
     <t>string</t>
@@ -56,19 +68,31 @@
     <t>帖子唯一ID</t>
   </si>
   <si>
-    <t>章节ID（对齐 chapters.id）</t>
-  </si>
-  <si>
-    <t>绑定关卡ID（发帖时间运行时读 levels.text2）</t>
-  </si>
-  <si>
-    <t>帖子正文</t>
-  </si>
-  <si>
-    <t>配图路径（res://）</t>
-  </si>
-  <si>
-    <t>头像路径（res://）</t>
+    <t>901=艺人 902=粉丝</t>
+  </si>
+  <si>
+    <t>可见性条件ID</t>
+  </si>
+  <si>
+    <t>点图进关</t>
+  </si>
+  <si>
+    <t>显示名</t>
+  </si>
+  <si>
+    <t>时间</t>
+  </si>
+  <si>
+    <t>正文</t>
+  </si>
+  <si>
+    <t>头像路径</t>
+  </si>
+  <si>
+    <t>主图</t>
+  </si>
+  <si>
+    <t>副图</t>
   </si>
   <si>
     <t>ch1_1_post</t>
@@ -77,13 +101,22 @@
     <t>ch1_l01</t>
   </si>
   <si>
-    <t>练习室日常一条。</t>
-  </si>
-  <si>
-    <t>res://art/feed/placeholder_post.png</t>
-  </si>
-  <si>
-    <t>res://art/feed/placeholder_avatar.png</t>
+    <t>Lee</t>
+  </si>
+  <si>
+    <t>02.14.2026</t>
+  </si>
+  <si>
+    <t>一个人的情人节,晚上见！</t>
+  </si>
+  <si>
+    <t>res://art/post/artist1.png</t>
+  </si>
+  <si>
+    <t>res://art/post/artist101.png</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>ch1_2_post</t>
@@ -92,6 +125,9 @@
     <t>ch1_l02</t>
   </si>
   <si>
+    <t>04.30.2023</t>
+  </si>
+  <si>
     <t>后台走廊线索。</t>
   </si>
   <si>
@@ -101,6 +137,9 @@
     <t>ch1_l03</t>
   </si>
   <si>
+    <t>04.30.2024</t>
+  </si>
+  <si>
     <t>后台走廊2。</t>
   </si>
   <si>
@@ -110,6 +149,9 @@
     <t>ch1_l04</t>
   </si>
   <si>
+    <t>04.30.2025</t>
+  </si>
+  <si>
     <t>后台走廊3。</t>
   </si>
   <si>
@@ -119,37 +161,25 @@
     <t>ch1_l05</t>
   </si>
   <si>
+    <t>04.30.2026</t>
+  </si>
+  <si>
     <t>后台走廊4（章末关）。</t>
   </si>
   <si>
-    <t>ch2_1_post</t>
-  </si>
-  <si>
-    <t>ch2_201</t>
-  </si>
-  <si>
-    <t>ch2_2_post</t>
-  </si>
-  <si>
-    <t>ch2_202</t>
-  </si>
-  <si>
-    <t>ch2_3_post</t>
-  </si>
-  <si>
-    <t>ch2_203</t>
-  </si>
-  <si>
-    <t>ch2_4_post</t>
-  </si>
-  <si>
-    <t>ch2_204</t>
-  </si>
-  <si>
-    <t>ch2_5_post</t>
-  </si>
-  <si>
-    <t>ch2_205</t>
+    <t>fanspost1</t>
+  </si>
+  <si>
+    <t>momo</t>
+  </si>
+  <si>
+    <t>期待期待！冲啊！Brave第一个出个人单曲的含金量！！</t>
+  </si>
+  <si>
+    <t>fanspost2</t>
+  </si>
+  <si>
+    <t>期待晚上的情人节和老公见面！Leo我爱你！</t>
   </si>
 </sst>
 </file>
@@ -763,11 +793,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1114,15 +1141,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="21.4545454545455" customWidth="1"/>
-    <col min="3" max="3" width="13.6363636363636" customWidth="1"/>
-    <col min="4" max="4" width="36.5454545454545" customWidth="1"/>
+    <col min="1" max="1" width="12.5454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1141,245 +1166,290 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
+        <v>901</v>
+      </c>
+      <c r="C4">
+        <v>4001</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
+        <v>901</v>
+      </c>
+      <c r="C5">
+        <v>4002</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
+        <v>901</v>
+      </c>
+      <c r="C6">
+        <v>4003</v>
       </c>
       <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
         <v>24</v>
       </c>
-      <c r="E6" t="s">
-        <v>17</v>
-      </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7">
+        <v>901</v>
+      </c>
+      <c r="C7">
+        <v>4004</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8">
+        <v>901</v>
+      </c>
+      <c r="C8">
+        <v>4005</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9">
+        <v>902</v>
+      </c>
+      <c r="C9">
+        <v>4001</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" t="s">
         <v>25</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="G9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" t="s">
         <v>27</v>
       </c>
-      <c r="E7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
+        <v>902</v>
+      </c>
+      <c r="C10">
+        <v>4001</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" t="s">
         <v>27</v>
-      </c>
-      <c r="E12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
